--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12A5CB0-B7AA-E548-96E6-B277AF67FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0EF5C6A-5302-6E46-BF40-6888F151F273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44440" yWindow="1000" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="1" r:id="rId1"/>
@@ -2256,22 +2256,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2286,6 +2274,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
@@ -2293,7 +2293,7 @@
     <cellStyle name="Normal 11 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -20852,7 +20852,7 @@
         <v>13</v>
       </c>
       <c r="E613" t="s">
-        <v>535</v>
+        <v>39</v>
       </c>
       <c r="F613" t="s">
         <v>14</v>
@@ -21300,7 +21300,7 @@
         <v>13</v>
       </c>
       <c r="E632" t="s">
-        <v>535</v>
+        <v>39</v>
       </c>
       <c r="F632" t="s">
         <v>14</v>
@@ -21389,10 +21389,10 @@
       <c r="C4" s="38" t="s">
         <v>430</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="52" t="s">
         <v>395</v>
       </c>
-      <c r="E4" s="57"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="39" t="s">
         <v>396</v>
       </c>
@@ -21407,10 +21407,10 @@
       <c r="C5" s="38">
         <v>5.5</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="54">
         <v>2.5</v>
       </c>
-      <c r="E5" s="59"/>
+      <c r="E5" s="55"/>
       <c r="F5" s="38" t="s">
         <v>397</v>
       </c>
@@ -21422,9 +21422,9 @@
       <c r="B6" s="49" t="s">
         <v>399</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="40" t="s">
         <v>400</v>
       </c>
@@ -21439,10 +21439,10 @@
       <c r="C7" s="38">
         <v>20</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="54">
         <v>20</v>
       </c>
-      <c r="E7" s="59"/>
+      <c r="E7" s="55"/>
       <c r="F7" s="38" t="s">
         <v>396</v>
       </c>
@@ -21457,10 +21457,10 @@
       <c r="C8" s="38">
         <v>3</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="54">
         <v>7</v>
       </c>
-      <c r="E8" s="59"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="38" t="s">
         <v>403</v>
       </c>
@@ -21472,9 +21472,9 @@
       <c r="B9" s="49" t="s">
         <v>431</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="40" t="s">
         <v>405</v>
       </c>
@@ -21546,7 +21546,7 @@
       <c r="D13" s="49">
         <v>23.6</v>
       </c>
-      <c r="E13" s="50"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="38" t="s">
         <v>408</v>
       </c>
@@ -21559,8 +21559,8 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="C14" s="45"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="52"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57"/>
       <c r="F14" s="40" t="s">
         <v>413</v>
       </c>
@@ -21578,7 +21578,7 @@
       <c r="D15" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="E15" s="50"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="38" t="s">
         <v>410</v>
       </c>
@@ -21596,7 +21596,7 @@
       <c r="D16" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="38" t="s">
         <v>396</v>
       </c>
@@ -21611,27 +21611,27 @@
       <c r="C17" s="39" t="s">
         <v>424</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="58" t="s">
         <v>425</v>
       </c>
-      <c r="E17" s="54"/>
+      <c r="E17" s="59"/>
       <c r="F17" s="40" t="s">
         <v>426</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
